--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EE512E-68D8-47DE-B572-7CF03B6EC000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4554346E-67E0-49F0-9047-B63BD662B380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -309,12 +309,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -329,11 +341,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -676,14 +690,14 @@
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -731,36 +745,36 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1088,14 +1102,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>39</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4554346E-67E0-49F0-9047-B63BD662B380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005FC1D9-85DA-45AA-AB57-9A95DD03C90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -309,7 +309,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -319,12 +319,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,13 +335,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -756,14 +749,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>51</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005FC1D9-85DA-45AA-AB57-9A95DD03C90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D01D702-3D51-4A0E-8E55-DF7F57F97E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -716,14 +716,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D01D702-3D51-4A0E-8E55-DF7F57F97E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB995AFA-82E1-4900-BEC5-3896C62623F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -675,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -771,25 +771,25 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -837,14 +837,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1133,14 +1133,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>76</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B46" t="s">
         <v>74</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C46" t="s">
         <v>75</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB995AFA-82E1-4900-BEC5-3896C62623F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3B4BCA-B7B4-45F9-BAC2-339CA1BCDA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -804,14 +804,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3B4BCA-B7B4-45F9-BAC2-339CA1BCDA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89409B7A-D6D4-451C-81B9-89E05D2BA4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>S11 / S40 / RE80</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>su 42</t>
   </si>
 </sst>
 </file>
@@ -323,7 +329,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -331,16 +337,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -675,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -683,7 +727,7 @@
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
         <v>1</v>
       </c>
@@ -693,8 +737,11 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -705,7 +752,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -716,7 +763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -726,8 +773,11 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -738,7 +788,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -748,8 +798,11 @@
       <c r="C6" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -759,8 +812,11 @@
       <c r="C7" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -770,8 +826,11 @@
       <c r="C8" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -781,8 +840,11 @@
       <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -792,8 +854,11 @@
       <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -804,7 +869,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -814,8 +879,11 @@
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -826,7 +894,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -837,7 +905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -847,8 +915,11 @@
       <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1035,7 +1106,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>33</v>
       </c>
@@ -1046,7 +1117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>34</v>
       </c>
@@ -1057,7 +1128,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>35</v>
       </c>
@@ -1068,7 +1139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>36</v>
       </c>
@@ -1079,7 +1150,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>37</v>
       </c>
@@ -1090,12 +1161,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -1105,8 +1176,11 @@
       <c r="C39" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>40</v>
       </c>
@@ -1117,23 +1191,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="42" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
         <v>42</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D43" s="4">
+        <f>COUNTIF(D1:D42,"ok")</f>
+        <v>10</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>76</v>
       </c>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89409B7A-D6D4-451C-81B9-89E05D2BA4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB598527-6D67-4F84-8C0B-57ABEA53B158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="85">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -293,7 +293,7 @@
     <t>ok</t>
   </si>
   <si>
-    <t>su 42</t>
+    <t>su 40</t>
   </si>
 </sst>
 </file>
@@ -1106,15 +1106,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>33</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1210,7 +1213,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB598527-6D67-4F84-8C0B-57ABEA53B158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AA2ECF-CEE9-4C19-AD70-022D007E1E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>su 40</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -1119,6 +1122,9 @@
       <c r="D33" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="E33" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
@@ -1181,6 +1187,9 @@
       </c>
       <c r="D39" s="2" t="s">
         <v>83</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AA2ECF-CEE9-4C19-AD70-022D007E1E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44588608-63FB-46A3-BB2C-9CE8E7D1A3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -318,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,6 +328,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -388,6 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1122,7 +1129,7 @@
       <c r="D33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="6" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1159,15 +1166,21 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>37</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1188,9 +1201,6 @@
       <c r="D39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
@@ -1222,7 +1232,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44588608-63FB-46A3-BB2C-9CE8E7D1A3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54440420-4844-4FF9-AFDF-4814E4771878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -1179,7 +1179,7 @@
       <c r="D37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="2" t="s">
         <v>85</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54440420-4844-4FF9-AFDF-4814E4771878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32036ED-CA52-4D23-8F25-018F3A07E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -318,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,12 +328,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -394,7 +388,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1129,7 +1122,7 @@
       <c r="D33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="2" t="s">
         <v>85</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32036ED-CA52-4D23-8F25-018F3A07E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2611DF40-8347-4319-A5E6-94459FE8759C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>su 40</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -1122,9 +1119,6 @@
       <c r="D33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
@@ -1171,9 +1165,6 @@
       </c>
       <c r="D37" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2611DF40-8347-4319-A5E6-94459FE8759C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15E7E40-D280-4C91-8F98-1DD1593A067A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>su 40</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -315,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +328,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -385,6 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -727,7 +737,7 @@
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
         <v>1</v>
       </c>
@@ -741,7 +751,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -752,7 +762,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -763,7 +773,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -777,7 +787,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -788,7 +798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -802,7 +812,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -816,7 +826,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -830,7 +840,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -844,7 +854,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -858,7 +868,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -869,7 +879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -883,7 +893,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -894,18 +904,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -919,7 +935,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1216,7 +1232,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15E7E40-D280-4C91-8F98-1DD1593A067A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EA40C2-95C6-409E-9254-009024F54DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -293,10 +293,13 @@
     <t>ok</t>
   </si>
   <si>
-    <t>su 40</t>
-  </si>
-  <si>
     <t>CHECK</t>
+  </si>
+  <si>
+    <t>SOOLO BUS</t>
+  </si>
+  <si>
+    <t>su 39</t>
   </si>
 </sst>
 </file>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +337,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -735,6 +745,7 @@
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="97.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -893,15 +904,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -918,7 +932,7 @@
         <v>83</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -935,15 +949,21 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1232,10 +1252,10 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EA40C2-95C6-409E-9254-009024F54DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2E54E5-A118-4E41-8FA1-3D7329C2A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -293,13 +293,10 @@
     <t>ok</t>
   </si>
   <si>
-    <t>CHECK</t>
-  </si>
-  <si>
-    <t>SOOLO BUS</t>
-  </si>
-  <si>
     <t>su 39</t>
+  </si>
+  <si>
+    <t>SOLO BUS</t>
   </si>
 </sst>
 </file>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,12 +328,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -904,17 +894,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+    <row r="13" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
         <v>13</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>85</v>
       </c>
     </row>
@@ -931,9 +921,6 @@
       <c r="D14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
@@ -961,9 +948,6 @@
       </c>
       <c r="D16" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1255,7 +1239,7 @@
         <v>14</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2E54E5-A118-4E41-8FA1-3D7329C2A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FE9662-A0C6-4FF1-B88E-B1A065082AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
   <si>
     <t>su 39</t>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,6 +331,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -894,18 +904,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>85</v>
+      <c r="E13" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -950,7 +960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,18 +971,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -983,7 +999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -994,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1005,7 +1021,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1016,7 +1032,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1027,7 +1043,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1038,7 +1054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1060,7 +1076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1071,7 +1087,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1082,7 +1098,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1093,7 +1109,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1115,7 +1131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1236,10 +1252,10 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FE9662-A0C6-4FF1-B88E-B1A065082AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5832BF6-8D1E-481D-BF82-5B900DC0152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -984,19 +984,22 @@
       <c r="D18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1252,7 +1255,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>85</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5832BF6-8D1E-481D-BF82-5B900DC0152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC53EAA-5E30-4F71-B3C5-7B12B37C46EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>ok</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
   <si>
     <t>su 39</t>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,12 +328,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -904,18 +894,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+    <row r="13" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
         <v>13</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>86</v>
+      <c r="E13" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -960,7 +950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -971,7 +961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -985,7 +975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -998,11 +988,8 @@
       <c r="D19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1013,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1024,7 +1011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1035,7 +1022,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1046,7 +1033,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1057,7 +1044,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1068,7 +1055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1079,7 +1066,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1090,7 +1077,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1101,7 +1088,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1112,7 +1099,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1123,7 +1110,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1134,7 +1121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1258,7 +1245,7 @@
         <v>16</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC53EAA-5E30-4F71-B3C5-7B12B37C46EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA541DD-2102-4A95-A21D-D15446CEE4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>SOLO BUS</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +337,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -950,7 +960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -975,7 +985,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -989,7 +999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1000,18 +1010,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1022,7 +1038,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1033,7 +1049,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1044,7 +1060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1055,7 +1071,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1066,7 +1082,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1077,7 +1093,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1088,7 +1104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1099,7 +1115,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1110,7 +1126,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1121,7 +1137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1242,7 +1258,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA541DD-2102-4A95-A21D-D15446CEE4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD27BD08-2E7E-4C0F-86A0-D822CE885388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>SOLO BUS</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,12 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -960,7 +950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -971,7 +961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -985,7 +975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -999,7 +989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1010,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1023,11 +1013,8 @@
       <c r="D21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1038,7 +1025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1049,7 +1036,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1060,7 +1047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1071,7 +1058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1082,7 +1069,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1093,7 +1080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1104,7 +1091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1115,7 +1102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1126,7 +1113,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1137,7 +1124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD27BD08-2E7E-4C0F-86A0-D822CE885388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D235BA0B-23AF-4514-9F5A-E9AF2AB8D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>SOLO BUS</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +337,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -950,7 +960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -975,7 +985,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -989,7 +999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1000,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1014,7 +1024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1025,18 +1035,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1047,7 +1063,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1058,7 +1074,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1069,7 +1085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1080,7 +1096,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1091,7 +1107,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1102,7 +1118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1113,7 +1129,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1124,7 +1140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1245,7 +1261,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D235BA0B-23AF-4514-9F5A-E9AF2AB8D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388833F1-4125-4DC3-9E14-36404B38B635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>SOLO BUS</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,12 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -960,7 +950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -971,7 +961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -985,7 +975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -999,7 +989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1010,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1024,7 +1014,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1035,7 +1025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1048,11 +1038,8 @@
       <c r="D23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1063,7 +1050,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1074,7 +1061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1085,7 +1072,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1096,7 +1083,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1107,7 +1094,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1118,7 +1105,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1129,7 +1116,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1140,7 +1127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388833F1-4125-4DC3-9E14-36404B38B635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846D1381-9F85-4270-A8E9-678BE1F074F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>SOLO BUS</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +337,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -950,7 +960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -975,7 +985,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -989,7 +999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1000,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1014,7 +1024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1025,7 +1035,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1039,18 +1049,24 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1061,7 +1077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1072,7 +1088,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1083,7 +1099,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1094,7 +1110,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1105,7 +1121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1116,7 +1132,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1127,7 +1143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1248,7 +1264,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846D1381-9F85-4270-A8E9-678BE1F074F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B272CA1-38DE-403E-B5C9-DFE7D203FD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>SOLO BUS</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,12 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -960,7 +950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -971,7 +961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -985,7 +975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -999,7 +989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1010,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1024,7 +1014,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1035,7 +1025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1049,7 +1039,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -1062,11 +1052,8 @@
       <c r="D24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1077,7 +1064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1088,7 +1075,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1099,7 +1086,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1110,7 +1097,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1121,7 +1108,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1132,7 +1119,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1143,7 +1130,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B272CA1-38DE-403E-B5C9-DFE7D203FD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9087E7-2038-4621-9A39-B0F476807880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>SOLO BUS</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -318,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +337,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -950,7 +960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -975,7 +985,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -989,7 +999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1000,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1014,7 +1024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1025,7 +1035,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1039,7 +1049,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -1053,7 +1063,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1064,7 +1074,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1075,29 +1085,41 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="D27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1108,7 +1130,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1119,7 +1141,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1130,7 +1152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1251,7 +1273,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9087E7-2038-4621-9A39-B0F476807880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04D073B-EA73-4E1E-8494-7EFA4E6F3A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>SOLO BUS</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -321,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,12 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -404,7 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -960,7 +950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -971,7 +961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -985,7 +975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -999,7 +989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1010,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1024,7 +1014,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1035,7 +1025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1049,7 +1039,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -1063,7 +1053,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1074,7 +1064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1085,7 +1075,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -1098,11 +1088,8 @@
       <c r="D27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -1115,11 +1102,8 @@
       <c r="D28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1130,7 +1114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1141,7 +1125,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1152,7 +1136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04D073B-EA73-4E1E-8494-7EFA4E6F3A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16334B7-D0C8-4245-BBAE-4C90675E11B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>SOLO BUS</t>
+  </si>
+  <si>
+    <t>non si capice</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -318,7 +324,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +340,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,6 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -735,7 +748,7 @@
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="97.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -950,7 +963,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -961,7 +974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -975,7 +988,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -989,7 +1002,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1000,7 +1013,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1014,7 +1027,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1025,7 +1038,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1039,7 +1052,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -1053,7 +1066,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1064,18 +1077,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -1089,7 +1105,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -1103,18 +1119,21 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1125,7 +1144,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1136,15 +1155,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="32" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>32</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1227,15 +1252,21 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="40" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>40</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1257,7 +1288,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <f>COUNTIF(D1:D42,"ok")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>84</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16334B7-D0C8-4245-BBAE-4C90675E11B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677DC42A-D591-4545-A7F8-4D4DFD2782CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -300,9 +300,6 @@
   </si>
   <si>
     <t>non si capice</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -1168,9 +1165,6 @@
       <c r="D32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
@@ -1264,9 +1258,6 @@
       </c>
       <c r="D40" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677DC42A-D591-4545-A7F8-4D4DFD2782CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2593D6DE-D0E0-4D59-B3F7-FDFD070D2809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -739,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1227,72 +1227,62 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>38</v>
+    <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>40</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>83</v>
+    <row r="40" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>78</v>
+      <c r="D41" s="4">
+        <f>COUNTIF(D1:D40,"ok")</f>
+        <v>23</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D43" s="4">
-        <f>COUNTIF(D1:D42,"ok")</f>
-        <v>23</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A43" t="s">
         <v>76</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B43" t="s">
         <v>74</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C43" t="s">
         <v>75</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2593D6DE-D0E0-4D59-B3F7-FDFD070D2809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B0E76-43C1-410D-809E-270ABAE2E0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -272,18 +272,9 @@
     <t>tilo</t>
   </si>
   <si>
-    <t>Biasca - Bellinzona - Lugano - Varese - Malpensa</t>
-  </si>
-  <si>
-    <t>S50</t>
-  </si>
-  <si>
     <t>Luino - Gallarate – Milano / Cadenazzo - Luino - Gallarate</t>
   </si>
   <si>
-    <t>R12 / S30</t>
-  </si>
-  <si>
     <t>Como - Milano - Rho / Como - Mendrisio - Varese / Chiasso - Milano Centrale</t>
   </si>
   <si>
@@ -293,13 +284,19 @@
     <t>ok</t>
   </si>
   <si>
-    <t>su 39</t>
-  </si>
-  <si>
     <t>SOLO BUS</t>
   </si>
   <si>
     <t>non si capice</t>
+  </si>
+  <si>
+    <t>R21 / S30</t>
+  </si>
+  <si>
+    <t>su 38</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -347,21 +344,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -394,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -402,7 +390,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -739,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -759,18 +746,24 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>71</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -795,18 +788,24 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
+      <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -814,13 +813,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -834,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -848,7 +847,7 @@
         <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -862,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -876,7 +875,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -901,21 +900,21 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>85</v>
+      <c r="E13" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -929,7 +928,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -943,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -957,7 +956,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,7 +981,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -996,7 +995,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1021,7 +1020,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1046,7 +1045,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1060,7 +1059,7 @@
         <v>41</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1074,18 +1073,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
         <v>26</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>86</v>
+      <c r="E26" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1099,7 +1098,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1113,21 +1112,21 @@
         <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
         <v>29</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>86</v>
+      <c r="E29" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1163,7 +1162,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1177,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,7 +1223,7 @@
         <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1238,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1252,37 +1251,26 @@
         <v>61</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="4">
-        <f>COUNTIF(D1:D40,"ok")</f>
-        <v>23</v>
-      </c>
-      <c r="E41" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D40" s="3">
+        <f>COUNTIF(D1:D39,"ok")</f>
+        <v>25</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>76</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B42" t="s">
         <v>74</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C42" t="s">
         <v>75</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B0E76-43C1-410D-809E-270ABAE2E0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA86DE3-2974-44D6-895D-054212A253C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>su 38</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -762,9 +759,6 @@
       <c r="D2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -803,9 +797,6 @@
       </c>
       <c r="D5" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA86DE3-2974-44D6-895D-054212A253C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39EAB66-88C4-4DA5-9193-E6F170A23085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -131,18 +131,9 @@
     <t>R6</t>
   </si>
   <si>
-    <t>Domodossola - Milano / Domodossola - Arona - Gallarate - Milano / Laveno – Sesto Calende</t>
-  </si>
-  <si>
-    <t>RE4 / R23 / R24</t>
-  </si>
-  <si>
     <t>Bergamo - Brescia / Lecco - Bergamo</t>
   </si>
   <si>
-    <t>R1 / R7</t>
-  </si>
-  <si>
     <t>Mortara - Alessandria / Mortara - Milano</t>
   </si>
   <si>
@@ -294,6 +285,18 @@
   </si>
   <si>
     <t>su 38</t>
+  </si>
+  <si>
+    <t>Domodossola - Milano / Domodossola - Arona - Gallarate - Milano</t>
+  </si>
+  <si>
+    <t>RE4 / R23</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>R1</t>
   </si>
 </sst>
 </file>
@@ -743,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -751,24 +754,30 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
+      <c r="B3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -782,7 +791,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -790,13 +799,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -804,13 +813,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -818,13 +827,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -832,13 +841,13 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -852,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -866,18 +875,24 @@
         <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -891,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -899,13 +914,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -919,7 +934,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -933,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -947,7 +962,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -972,7 +987,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -986,7 +1001,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1005,13 +1020,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1019,10 +1034,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1030,13 +1045,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1044,13 +1059,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1058,10 +1073,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1069,13 +1084,13 @@
         <v>26</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1083,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1097,13 +1112,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1111,13 +1126,13 @@
         <v>29</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1125,10 +1140,10 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,13 +1162,13 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1167,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,10 +1190,10 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,10 +1212,10 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1208,13 +1223,13 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1222,13 +1237,13 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1236,37 +1251,38 @@
         <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="3">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39EAB66-88C4-4DA5-9193-E6F170A23085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A23E48-A6AE-4B1F-B0FC-A099E2401D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>RE4 / R23</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
   <si>
     <t>R1</t>
@@ -776,9 +773,6 @@
       <c r="D3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
@@ -886,13 +880,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A23E48-A6AE-4B1F-B0FC-A099E2401D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57387E73-39B5-4FBB-A785-7B1808B198C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>R1</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -381,14 +384,14 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -732,266 +735,269 @@
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="D2" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="D3" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="D4" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="D6" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="D9" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="D10" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="D11" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>13</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="D14" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="D15" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>16</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="D16" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>17</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="E17" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>18</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="D18" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1006,17 +1012,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>21</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1031,31 +1037,31 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+    <row r="23" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="D23" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>24</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1070,59 +1076,59 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>26</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+    <row r="27" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>27</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="D27" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
+      <c r="D28" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1148,31 +1154,31 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+    <row r="32" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
         <v>32</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="D32" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>33</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1209,54 +1215,54 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>37</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>39</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="D38" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>40</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D40" s="3">
+      <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
         <v>27</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>81</v>
       </c>
     </row>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57387E73-39B5-4FBB-A785-7B1808B198C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73C9E7C-4920-4181-B86E-B0DFA80802A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="86">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -969,6 +969,9 @@
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="E17" s="5" t="s">
         <v>85</v>
       </c>
@@ -1260,7 +1263,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>81</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73C9E7C-4920-4181-B86E-B0DFA80802A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD564E7-8ED5-4134-881B-81813D7C0199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -254,15 +254,6 @@
     <t>RE3 / R3 / R9 / S34</t>
   </si>
   <si>
-    <t>Biasca - Bellinzona - Lugano - Chiasso - Como San Giovanni</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>tilo</t>
-  </si>
-  <si>
     <t>Luino - Gallarate – Milano / Cadenazzo - Luino - Gallarate</t>
   </si>
   <si>
@@ -294,9 +285,6 @@
   </si>
   <si>
     <t>R1</t>
-  </si>
-  <si>
-    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -726,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -746,7 +734,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -760,7 +748,7 @@
         <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -768,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -788,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -796,13 +784,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -810,13 +798,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -830,7 +818,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -844,7 +832,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -858,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -872,7 +860,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -883,10 +871,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -900,7 +888,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -914,7 +902,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -928,7 +916,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -942,7 +930,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -956,7 +944,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -970,10 +958,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -987,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1001,7 +986,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1026,7 +1011,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1051,7 +1036,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1065,7 +1050,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1090,7 +1075,7 @@
         <v>34</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1104,7 +1089,7 @@
         <v>42</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1118,7 +1103,7 @@
         <v>40</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -1132,7 +1117,7 @@
         <v>54</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1168,7 +1153,7 @@
         <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1182,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1229,7 +1214,7 @@
         <v>56</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1243,7 +1228,7 @@
         <v>62</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1257,7 +1242,7 @@
         <v>58</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,18 +1251,7 @@
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD564E7-8ED5-4134-881B-81813D7C0199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3C3A72-0855-4CDD-BACE-544DC3139320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>R1</t>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
 </sst>
 </file>
@@ -1131,15 +1134,21 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="31" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
         <v>31</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1192,15 +1201,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1248,7 +1260,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3C3A72-0855-4CDD-BACE-544DC3139320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E333B9-A778-4928-91C7-258B8099717B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -287,7 +287,7 @@
     <t>R1</t>
   </si>
   <si>
-    <t>CHECK</t>
+    <t>RE13 e R33 boh</t>
   </si>
 </sst>
 </file>
@@ -723,7 +723,7 @@
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="97.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1017,15 +1017,21 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1147,9 +1153,6 @@
       <c r="D31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="32" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -1260,7 +1263,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E333B9-A778-4928-91C7-258B8099717B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD303D1B-7CB4-4C86-B6BC-E5B161B9F89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>RE13 e R33 boh</t>
+  </si>
+  <si>
+    <t>R39 e R40 boh</t>
   </si>
 </sst>
 </file>
@@ -992,15 +995,21 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>27</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1263,7 +1272,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD303D1B-7CB4-4C86-B6BC-E5B161B9F89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9E97EC-F6AE-4784-8586-480DF814296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -287,10 +287,19 @@
     <t>R1</t>
   </si>
   <si>
+    <t>CHECK</t>
+  </si>
+  <si>
     <t>RE13 e R33 boh</t>
   </si>
   <si>
     <t>R39 e R40 boh</t>
+  </si>
+  <si>
+    <t>R32 boh</t>
+  </si>
+  <si>
+    <t>check</t>
   </si>
 </sst>
 </file>
@@ -720,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BE5C4-52B3-4A8B-9EE7-686436176D81}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -953,7 +962,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -967,7 +976,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -981,7 +990,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -995,7 +1004,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>20</v>
       </c>
@@ -1009,10 +1018,10 @@
         <v>74</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -1026,7 +1035,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -1040,10 +1049,10 @@
         <v>74</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -1057,7 +1066,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -1071,18 +1080,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>26</v>
       </c>
@@ -1096,7 +1114,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -1110,7 +1128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -1124,7 +1142,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>29</v>
       </c>
@@ -1138,18 +1156,24 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>30</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -1163,7 +1187,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -1272,7 +1296,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9E97EC-F6AE-4784-8586-480DF814296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9273B500-2742-46DA-89C1-50AB639909F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -1226,15 +1226,21 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>35</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1296,7 +1302,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>

--- a/direttrici/direttrici.xlsx
+++ b/direttrici/direttrici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommaso\.gemini\antigravity\scratch\monitor_treni\direttrici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9273B500-2742-46DA-89C1-50AB639909F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EBE33F-F018-4058-BD47-E4520DC03AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C15CDBC-8405-45FA-BA7F-E008D9D76093}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="88">
   <si>
     <t>Novara - Milano Passante - Treviglio</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>check</t>
+  </si>
+  <si>
+    <t>RE3,R3,R9 boh</t>
   </si>
 </sst>
 </file>
@@ -734,7 +737,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="97.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1201,7 +1204,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -1215,18 +1218,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
         <v>34</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -1243,7 +1255,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -1257,7 +1269,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -1271,7 +1283,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>39</v>
       </c>
@@ -1285,7 +1297,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>40</v>
       </c>
@@ -1299,10 +1311,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D40" s="2">
         <f>COUNTIF(D1:D39,"ok")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>78</v>
